--- a/knowledge-base.xlsx
+++ b/knowledge-base.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="К передаче (21 задача)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Все задачи'!$A$1:$N$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Все задачи'!$A$1:$N$303</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Выполненные задачи'!$A$1:$N$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'К передаче (21 задача)'!$A$2:$G$2</definedName>
   </definedNames>
@@ -846,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N297"/>
+  <dimension ref="A1:N303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19310,7 +19310,7 @@
       </c>
       <c r="N251" s="12" t="inlineStr">
         <is>
-          <t>Согласование / В работе (10.07.2026)</t>
+          <t>В РАБОТЕ (21.07.2026) — активная обработка (Колдин О.В., Федоров С.И., доп. информация). Ранее: Согласование / В работе (10.07.2026)</t>
         </is>
       </c>
     </row>
@@ -19896,7 +19896,7 @@
       </c>
       <c r="N259" s="12" t="inlineStr">
         <is>
-          <t>НАЗНАЧЕН (19.07.2026) — исполнитель Мархотина С.И.</t>
+          <t>В РАБОТЕ (21.07.2026) — комментарии Стаценко М.И. (20.07) и Ельшиной Ю.А. (реестр возвратов ДАНДА, МОРы проведены). Ранее: НАЗНАЧЕН (19.07.2026) — Мархотина С.И.</t>
         </is>
       </c>
     </row>
@@ -22583,12 +22583,445 @@
         </is>
       </c>
     </row>
-    <row r="298" ht="36" customHeight="1"/>
-    <row r="299" ht="51.75" customHeight="1"/>
-    <row r="300" ht="51.75" customHeight="1"/>
-    <row r="301" ht="51.75" customHeight="1"/>
-    <row r="302" ht="51.75" customHeight="1"/>
-    <row r="303" ht="51.75" customHeight="1"/>
+    <row r="298" ht="36" customHeight="1">
+      <c r="A298" s="14" t="inlineStr">
+        <is>
+          <t>ARM-7060</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>Разбраковка по необоснованно отклонённым документам — расхождение остатков</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>Разработка 1С Склад / Инцидент</t>
+        </is>
+      </c>
+      <c r="D298" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="inlineStr">
+        <is>
+          <t>Стругов Д.Ю.</t>
+        </is>
+      </c>
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>Козырева К.В. (отдел претензий)</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr">
+        <is>
+          <t>ENT-9675</t>
+        </is>
+      </c>
+      <c r="H298" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I298" s="8" t="inlineStr">
+        <is>
+          <t>Задача создана Струговым Д.Ю. для извлечения документов, по которым прошло необоснованное отклонение (к задаче приложен список документов и файл БазаАВЕ). 20.07 Козырева К.В. запросила проверку, зачем проведена разбраковка при согласованном возврате и проведённой КСФ (код отказа 12). 21.07 Чернышев Р.В. пояснил, что разбраковка сделана по ARM-7060; Стаценко М.И. отметил расхождение остатков между аптекой и офисом, т.к. не все документы проведены в 1С Склад. Стругов не нашёл данных о запуске скрипта по спорному документу (ID 93f5fa…) — его нет ни в списке задачи, ни по номерам упаковок.</t>
+        </is>
+      </c>
+      <c r="J298" s="5" t="inlineStr">
+        <is>
+          <t>После разбраковки товар, которого фактически нет, встаёт на остатки аптеки; отдел претензий не знает, как списать несуществующий товар. Возникло расхождение остатков аптека/офис.</t>
+        </is>
+      </c>
+      <c r="K298" s="9" t="inlineStr">
+        <is>
+          <t>1) Уточнить, по какому документу прошла спорная разбраковка (ID 93f5fa…)
+2) Определить механизм списания товара, вставшего на остаток ошибочно
+3) Провести недостающие документы в 1С Склад для устранения расхождения
+4) При необходимости — встреча со Струговым Д.Ю.</t>
+        </is>
+      </c>
+      <c r="L298" s="10" t="inlineStr">
+        <is>
+          <t>https://jira.366.ru/browse/ARM-7060</t>
+        </is>
+      </c>
+      <c r="M298" s="11" t="inlineStr">
+        <is>
+          <t>inbox.json (Чернышев/Стругов/Козырева, 20–21.07.2026)</t>
+        </is>
+      </c>
+      <c r="N298" s="12" t="inlineStr">
+        <is>
+          <t>В РАБОТЕ / ЭСКАЛАЦИЯ (21.07.2026) — обсуждение механизма списания и расхождения остатков</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="51.75" customHeight="1">
+      <c r="A299" s="14" t="inlineStr">
+        <is>
+          <t>ENT-10925</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>Оповещение аптек по документам поступления с типом накладной «Сторно»</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>Разработка 1С Склад</t>
+        </is>
+      </c>
+      <c r="D299" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="inlineStr">
+        <is>
+          <t>Прикладовский А.А.</t>
+        </is>
+      </c>
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>Чернышев Р.В.</t>
+        </is>
+      </c>
+      <c r="G299" s="6" t="inlineStr">
+        <is>
+          <t>RPRD-2595</t>
+        </is>
+      </c>
+      <c r="H299" s="13" t="inlineStr">
+        <is>
+          <t>1 день (оценка Jira)</t>
+        </is>
+      </c>
+      <c r="I299" s="8" t="inlineStr">
+        <is>
+          <t>Задача в списке разработки 1С Склад: «Создать оповещение аптек по созданным документам поступление товаров и услуг с типом накладной "Сторно"». 21.07 Чернышев Р.В. приложил ТЗ (ТЗ_Оповещение_аптек_Сторно_МОР.docx); Прикладовский А.А. внёс изменения по задаче.</t>
+        </is>
+      </c>
+      <c r="J299" s="5" t="inlineStr">
+        <is>
+          <t>Требуется автоматическое оповещение аптек о созданных документах поступления с типом накладной «Сторно» (сторнирование МОР).</t>
+        </is>
+      </c>
+      <c r="K299" s="9" t="inlineStr">
+        <is>
+          <t>1) Реализовать оповещение аптек по документам поступления типа «Сторно»
+2) Использовать приложенное ТЗ (ТЗ_Оповещение_аптек_Сторно_МОР.docx)</t>
+        </is>
+      </c>
+      <c r="L299" s="10" t="inlineStr">
+        <is>
+          <t>https://jira.366.ru/browse/ENT-10925</t>
+        </is>
+      </c>
+      <c r="M299" s="11" t="inlineStr">
+        <is>
+          <t>inbox.json (Jira, 21.07.2026)</t>
+        </is>
+      </c>
+      <c r="N299" s="12" t="inlineStr">
+        <is>
+          <t>В РАЗРАБОТКЕ (Jira 2026.07.21) — оценка 1 день, ТЗ приложено</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="51.75" customHeight="1">
+      <c r="A300" s="14" t="inlineStr">
+        <is>
+          <t>SD #3951553</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>Обновить тестовую базу 1С:Склад (ave_skd_yak)</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>SD / ИТ инфраструктура</t>
+        </is>
+      </c>
+      <c r="D300" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="inlineStr">
+        <is>
+          <t>Егоров М.Д.</t>
+        </is>
+      </c>
+      <c r="F300" s="5" t="inlineStr">
+        <is>
+          <t>Квитко А.С.</t>
+        </is>
+      </c>
+      <c r="G300" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H300" s="13" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="I300" s="8" t="inlineStr">
+        <is>
+          <t>Заявка на обновление тестовой базы 1С:Склад (Srvr="tst-1csrv-03";Ref="ave_skd_yak"). 21.07 09:31 Егоров М.Д. приступил к работе; днём заявка переведена в статус «Отложен» — ожидается загрузка БД по связанной заявке. Сервер БД: pg-db-01-dev13.id-soft.network.</t>
+        </is>
+      </c>
+      <c r="J300" s="5" t="inlineStr">
+        <is>
+          <t>Обновление тестовой базы разработки 1С Склад из актуальной копии.</t>
+        </is>
+      </c>
+      <c r="K300" s="9" t="inlineStr">
+        <is>
+          <t>1) Дождаться загрузки БД
+2) Обновить тестовую базу ave_skd_yak</t>
+        </is>
+      </c>
+      <c r="L300" s="10" t="inlineStr">
+        <is>
+          <t>https://sd.366.ru/Task/view/3951553</t>
+        </is>
+      </c>
+      <c r="M300" s="11" t="inlineStr">
+        <is>
+          <t>inbox.json (IntraService, 21.07.2026)</t>
+        </is>
+      </c>
+      <c r="N300" s="12" t="inlineStr">
+        <is>
+          <t>ОТЛОЖЕН (21.07.2026) — ожидается загрузка БД; срок 28.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="51.75" customHeight="1">
+      <c r="A301" s="14" t="inlineStr">
+        <is>
+          <t>SD #3951563</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>Создать копию базы 1С Склад для разработчика</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>SD / ИТ инфраструктура</t>
+        </is>
+      </c>
+      <c r="D301" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="inlineStr">
+        <is>
+          <t>Егоров М.Д.</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="inlineStr">
+        <is>
+          <t>Квитко А.С.</t>
+        </is>
+      </c>
+      <c r="G301" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H301" s="13" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="I301" s="8" t="inlineStr">
+        <is>
+          <t>Заявка на создание копии базы 1С Склад для разработчика по аналогии с существующими (ave_skd_sokolov, ave_skd_samkir). 21.07 09:31 Егоров М.Д. приступил к работе; днём заявка переведена в статус «Отложен».</t>
+        </is>
+      </c>
+      <c r="J301" s="5" t="inlineStr">
+        <is>
+          <t>Нужна отдельная копия базы 1С Склад для работы разработчика.</t>
+        </is>
+      </c>
+      <c r="K301" s="9" t="inlineStr">
+        <is>
+          <t>1) Создать копию базы 1С Склад на tst-1csrv-03 по аналогии с ave_skd_sokolov / ave_skd_samkir</t>
+        </is>
+      </c>
+      <c r="L301" s="10" t="inlineStr">
+        <is>
+          <t>https://sd.366.ru/Task/view/3951563</t>
+        </is>
+      </c>
+      <c r="M301" s="11" t="inlineStr">
+        <is>
+          <t>inbox.json (IntraService, 21.07.2026)</t>
+        </is>
+      </c>
+      <c r="N301" s="12" t="inlineStr">
+        <is>
+          <t>ОТЛОЖЕН (21.07.2026) — срок 23.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="51.75" customHeight="1">
+      <c r="A302" s="14" t="inlineStr">
+        <is>
+          <t>SD #3528895</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>Добавить проверку загрузки файла dbf от поставщика на юр. лицо</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>SD / Изменение 1С Склад</t>
+        </is>
+      </c>
+      <c r="D302" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="inlineStr">
+        <is>
+          <t>Не назначен</t>
+        </is>
+      </c>
+      <c r="F302" s="5" t="inlineStr">
+        <is>
+          <t>Заявитель СД (Квитко А.С. — наблюдатель)</t>
+        </is>
+      </c>
+      <c r="G302" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H302" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I302" s="8" t="inlineStr">
+        <is>
+          <t>Квитко А.С. назначен наблюдателем на заявку (21.07). Суть: участились ошибки, когда поставщик указывает неверное юр. лицо в привязке к аптеке — как следствие: акты сверки с расхождением, несостыковки книг продаж/покупок (требования ИФНС), некорректные оплаты, разница во взаиморасчётах, неверные претензии, неверная привязка КСФ. Правки на стороне розничных юр. лиц невозможны (задействованы три базы + продажи розничному покупателю). Актуально в преддверии реорганизации.</t>
+        </is>
+      </c>
+      <c r="J302" s="5" t="inlineStr">
+        <is>
+          <t>Нет проверки соответствия юр. лица при загрузке dbf-файла от поставщика — ошибки привязки приводят к бухгалтерским и претензионным расхождениям.</t>
+        </is>
+      </c>
+      <c r="K302" s="9" t="inlineStr">
+        <is>
+          <t>1) Добавить проверку загрузки файла dbf от поставщика на корректное юр. лицо
+2) Блокировать/сигнализировать при несоответствии привязки аптека↔юр.лицо</t>
+        </is>
+      </c>
+      <c r="L302" s="10" t="inlineStr">
+        <is>
+          <t>https://sd.366.ru/Task/view/3528895</t>
+        </is>
+      </c>
+      <c r="M302" s="11" t="inlineStr">
+        <is>
+          <t>inbox.json (IntraService, 21.07.2026)</t>
+        </is>
+      </c>
+      <c r="N302" s="12" t="inlineStr">
+        <is>
+          <t>НАБЛЮДЕНИЕ (21.07.2026) — Квитко А.С. назначен наблюдателем</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="51.75" customHeight="1">
+      <c r="A303" s="14" t="inlineStr">
+        <is>
+          <t>SD #3935212</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>Аннулирование МОР по АП 1221 (Таганская)</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>SD / Инцидент 1С Склад</t>
+        </is>
+      </c>
+      <c r="D303" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="inlineStr">
+        <is>
+          <t>Не определён</t>
+        </is>
+      </c>
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>Беканов А.А. (через Михалеву Ю.А.)</t>
+        </is>
+      </c>
+      <c r="G303" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H303" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I303" s="8" t="inlineStr">
+        <is>
+          <t>20.07 Беканов А.А. попросил помочь с аннулированием пяти МОР по АП 1221 (Таганская ул., д.1 стр.1): 385/1221, 129/1221, 108/1221, 71/1221, 347/1221. МОР 401/1221, который в заявке, аннулировать не нужно — выгружен. Михалева Ю.А. переслала обращение с пометкой «Нужна помощь».</t>
+        </is>
+      </c>
+      <c r="J303" s="5" t="inlineStr">
+        <is>
+          <t>Требуется аннулировать пять ошибочных МОР по аптеке 1221, сохранив выгруженный МОР 401/1221.</t>
+        </is>
+      </c>
+      <c r="K303" s="9" t="inlineStr">
+        <is>
+          <t>1) Аннулировать МОР 385/1221, 129/1221, 108/1221, 71/1221, 347/1221
+2) НЕ аннулировать МОР 401/1221 (выгружен)</t>
+        </is>
+      </c>
+      <c r="L303" s="10" t="inlineStr">
+        <is>
+          <t>https://sd.366.ru/Task/view/3935212</t>
+        </is>
+      </c>
+      <c r="M303" s="11" t="inlineStr">
+        <is>
+          <t>inbox.json (Михалева/Беканов, 20.07.2026)</t>
+        </is>
+      </c>
+      <c r="N303" s="12" t="inlineStr">
+        <is>
+          <t>ПОСТУПИЛА / ТРЕБУЕТ ОБРАБОТКИ (20.07.2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="304" ht="51.75" customHeight="1"/>
     <row r="305" ht="51.75" customHeight="1"/>
     <row r="306" ht="51.75" customHeight="1"/>
@@ -22625,7 +23058,7 @@
     <row r="337" ht="51.75" customHeight="1"/>
     <row r="338" ht="51.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:N297"/>
+  <autoFilter ref="A1:N303"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
